--- a/testModel_Ninja/animations/Attack/攻撃パート.xlsx
+++ b/testModel_Ninja/animations/Attack/攻撃パート.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\testModel_Ninja\animations\Attack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\testModel_Ninja\animations\Attack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993A4A25-4220-4CEF-ADE2-7DF950328AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D0CE48-4195-4D63-B682-81B5C59B586E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7965" yWindow="3075" windowWidth="24810" windowHeight="17430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>弱攻撃</t>
     <rPh sb="0" eb="1">
@@ -115,6 +115,52 @@
       <t>ワザ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(地上連携)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切り上げ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（空中連携）</t>
+    <rPh sb="1" eb="3">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いずな落とし</t>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一旦パス</t>
+  </si>
+  <si>
+    <t>Yの位置で</t>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いろいろ連携あるが</t>
   </si>
 </sst>
 </file>
@@ -137,12 +183,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -157,8 +209,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -439,8 +492,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -492,24 +551,85 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E11" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/testModel_Ninja/animations/Attack/攻撃パート.xlsx
+++ b/testModel_Ninja/animations/Attack/攻撃パート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\testModel_Ninja\animations\Attack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D0CE48-4195-4D63-B682-81B5C59B586E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98BF48D-1FA9-4D9C-A175-1122587A5A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7965" yWindow="3075" windowWidth="24810" windowHeight="17430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25875" yWindow="3000" windowWidth="24810" windowHeight="17430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>弱攻撃</t>
     <rPh sb="0" eb="1">
@@ -161,6 +161,17 @@
   </si>
   <si>
     <t>いろいろ連携あるが</t>
+  </si>
+  <si>
+    <t>あまり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spin技</t>
+    <rPh sb="4" eb="5">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -492,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
@@ -501,7 +512,7 @@
     <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -520,8 +531,14 @@
       <c r="F1">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -538,7 +555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -549,12 +566,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -565,12 +582,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -587,7 +604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -595,12 +612,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -617,12 +634,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>

--- a/testModel_Ninja/animations/Attack/攻撃パート.xlsx
+++ b/testModel_Ninja/animations/Attack/攻撃パート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\testModel_Ninja\animations\Attack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\testModel_Ninja\animations\Attack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98BF48D-1FA9-4D9C-A175-1122587A5A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3E942F-5FB5-454F-95F1-315D60F9598F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25875" yWindow="3000" windowWidth="24810" windowHeight="17430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>弱攻撃</t>
     <rPh sb="0" eb="1">
@@ -44,20 +44,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>けり技1</t>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けり技2</t>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>締め技</t>
     <rPh sb="0" eb="1">
       <t>シ</t>
@@ -103,20 +89,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>技2</t>
-    <rPh sb="0" eb="1">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>技3</t>
-    <rPh sb="0" eb="1">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>(地上連携)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -171,6 +143,48 @@
     <rPh sb="4" eb="5">
       <t>ワザ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>airAttack1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>airAttack2</t>
+  </si>
+  <si>
+    <t>airAttack3</t>
+  </si>
+  <si>
+    <t>airAttack4</t>
+  </si>
+  <si>
+    <t>airAttack5</t>
+  </si>
+  <si>
+    <t>kick_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kick_2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>upAttack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>横切り技</t>
+    <rPh sb="0" eb="2">
+      <t>ヨコギ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X-&gt;Y</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -507,14 +521,12 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -532,10 +544,10 @@
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -546,107 +558,113 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
